--- a/information_request_forms/005_makeup_consultation_form--information_request_forms.xlsx
+++ b/information_request_forms/005_makeup_consultation_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1095,17 +1095,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>product_type_choices</t>
+          <t>desired_color_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>blush</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Blush</t>
+          <t>Pink</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Purple</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1151,29 +1151,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>desired_color_choices</t>
+          <t>skin_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>brown</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dry</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dry</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>oily</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oily</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -1219,29 +1219,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>combination</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Combination</t>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>skin_type_choices</t>
+          <t>face_shape_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sensitive</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sensitive</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
@@ -1287,29 +1287,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>face_shape_choices</t>
+          <t>eye_type_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>almond</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Heart</t>
+          <t>Almond</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>almond</t>
+          <t>avocado</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Almond</t>
+          <t>Avocado</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>avocado</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avocado</t>
+          <t>Diamond</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Heart</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1406,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>rounded</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Rounded</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>eye_type_choices</t>
+          <t>hair_type_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>rounded</t>
+          <t>curly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rounded</t>
+          <t>Curly</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>curly</t>
+          <t>straight</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Curly</t>
+          <t>Straight</t>
         </is>
       </c>
     </row>
@@ -1457,80 +1457,80 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>wavy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>Wavy</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hair_type_choices</t>
+          <t>hair_color_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wavy</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wavy</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hair_type_choices</t>
+          <t>hair_color_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>curly</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Curly</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hair_type_choices</t>
+          <t>hair_color_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>Blonde</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hair_type_choices</t>
+          <t>hair_color_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wavy</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wavy</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1542,146 +1542,78 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>brown</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Pink</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hair_color_choices</t>
+          <t>nail_type_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Natural</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hair_color_choices</t>
+          <t>nail_type_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>blonde</t>
+          <t>acrylic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Blonde</t>
+          <t>Acrylic</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hair_color_choices</t>
+          <t>nail_type_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>tip</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Tip</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hair_color_choices</t>
+          <t>nail_type_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>tipless</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>nail_type_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>nail_type_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>acrylic</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Acrylic</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>nail_type_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>tip</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>nail_type_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>tipless</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
         <is>
           <t>Tipless</t>
         </is>
